--- a/Data/2021_F013B4_CO_ISSWC/2021_F013B4_CO_ISSWC_CropCanopy.xlsx
+++ b/Data/2021_F013B4_CO_ISSWC/2021_F013B4_CO_ISSWC_CropCanopy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2021_F013B4_CO_ISSWC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE06B8D-7A46-4D4A-A3C2-6DC808FDBA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB6A50A-203B-4F8A-8333-95E1C021E20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1470" yWindow="-24510" windowWidth="17805" windowHeight="20370" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Height" sheetId="9" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3751" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3751" uniqueCount="448">
   <si>
     <t>01-</t>
   </si>
@@ -1425,9 +1425,6 @@
   </si>
   <si>
     <t>24 May &amp; 7 June</t>
-  </si>
-  <si>
-    <t>PLAPD</t>
   </si>
   <si>
     <t>Average</t>
@@ -2920,22 +2917,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="25" fillId="5" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="25" fillId="4" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="25" fillId="4" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="35" fillId="5" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2945,6 +2936,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="5" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="25" fillId="5" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -8828,19 +8825,19 @@
       </c>
       <c r="C11" s="192"/>
       <c r="D11" s="192"/>
-      <c r="E11" s="269" t="s">
+      <c r="E11" s="276" t="s">
         <v>347</v>
       </c>
       <c r="F11" s="270"/>
-      <c r="G11" s="274" t="s">
+      <c r="G11" s="269" t="s">
         <v>346</v>
       </c>
       <c r="H11" s="270"/>
-      <c r="I11" s="274">
+      <c r="I11" s="269">
         <v>44319</v>
       </c>
       <c r="J11" s="270"/>
-      <c r="K11" s="274">
+      <c r="K11" s="269">
         <v>44323</v>
       </c>
       <c r="L11" s="270"/>
@@ -8861,19 +8858,19 @@
       </c>
       <c r="C12" s="189"/>
       <c r="D12" s="189"/>
-      <c r="E12" s="271">
+      <c r="E12" s="277">
         <v>119</v>
       </c>
       <c r="F12" s="272"/>
-      <c r="G12" s="273">
+      <c r="G12" s="271">
         <v>122</v>
       </c>
       <c r="H12" s="272"/>
-      <c r="I12" s="273">
+      <c r="I12" s="271">
         <v>123</v>
       </c>
       <c r="J12" s="272"/>
-      <c r="K12" s="273">
+      <c r="K12" s="271">
         <v>127</v>
       </c>
       <c r="L12" s="272"/>
@@ -8894,19 +8891,19 @@
       </c>
       <c r="C13" s="185"/>
       <c r="D13" s="185"/>
-      <c r="E13" s="277" t="s">
+      <c r="E13" s="275" t="s">
         <v>51</v>
       </c>
       <c r="F13" s="272"/>
-      <c r="G13" s="277" t="s">
+      <c r="G13" s="275" t="s">
         <v>51</v>
       </c>
       <c r="H13" s="272"/>
-      <c r="I13" s="277" t="s">
+      <c r="I13" s="275" t="s">
         <v>51</v>
       </c>
       <c r="J13" s="272"/>
-      <c r="K13" s="277" t="s">
+      <c r="K13" s="275" t="s">
         <v>51</v>
       </c>
       <c r="L13" s="272"/>
@@ -8927,22 +8924,22 @@
       </c>
       <c r="C14" s="180"/>
       <c r="D14" s="180"/>
-      <c r="E14" s="275" t="s">
+      <c r="E14" s="273" t="s">
         <v>344</v>
       </c>
-      <c r="F14" s="276"/>
-      <c r="G14" s="275" t="s">
+      <c r="F14" s="274"/>
+      <c r="G14" s="273" t="s">
         <v>343</v>
       </c>
-      <c r="H14" s="276"/>
-      <c r="I14" s="275" t="s">
+      <c r="H14" s="274"/>
+      <c r="I14" s="273" t="s">
         <v>342</v>
       </c>
-      <c r="J14" s="276"/>
-      <c r="K14" s="275" t="s">
+      <c r="J14" s="274"/>
+      <c r="K14" s="273" t="s">
         <v>341</v>
       </c>
-      <c r="L14" s="276"/>
+      <c r="L14" s="274"/>
       <c r="M14" s="182" t="s">
         <v>340</v>
       </c>
@@ -15907,7 +15904,7 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G2" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -20203,7 +20200,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -20214,7 +20211,7 @@
     </row>
     <row r="4" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="279" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C4" s="281"/>
       <c r="D4" s="281"/>
@@ -20272,7 +20269,7 @@
         <v>30</v>
       </c>
       <c r="M6" s="258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -22200,7 +22197,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -22211,7 +22208,7 @@
     </row>
     <row r="4" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="279" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C4" s="281"/>
       <c r="D4" s="281"/>
@@ -22269,7 +22266,7 @@
         <v>30</v>
       </c>
       <c r="M6" s="258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -24197,7 +24194,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -24208,7 +24205,7 @@
     </row>
     <row r="4" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="279" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C4" s="281"/>
       <c r="D4" s="281"/>
@@ -24266,7 +24263,7 @@
         <v>30</v>
       </c>
       <c r="M6" s="258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -26194,7 +26191,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -26203,12 +26200,12 @@
         <v>51</v>
       </c>
       <c r="H3" s="265" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="279" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C4" s="281"/>
       <c r="D4" s="281"/>
@@ -26266,7 +26263,7 @@
         <v>30</v>
       </c>
       <c r="M6" s="258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -26776,7 +26773,7 @@
         <v>4.8888888888888893</v>
       </c>
       <c r="N19" s="50" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -26937,7 +26934,7 @@
         <v>5.7777777777777777</v>
       </c>
       <c r="N23" s="50" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -27096,7 +27093,7 @@
         <v>5.8888888888888893</v>
       </c>
       <c r="N27" s="50" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -27255,7 +27252,7 @@
         <v>5.7777777777777777</v>
       </c>
       <c r="N31" s="50" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -27570,7 +27567,7 @@
         <v>5.4444444444444446</v>
       </c>
       <c r="N39" s="50" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="40" spans="2:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -28041,7 +28038,7 @@
         <v>4.4444444444444446</v>
       </c>
       <c r="N51" s="50" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -28212,7 +28209,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -28223,7 +28220,7 @@
     </row>
     <row r="4" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="279" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C4" s="281"/>
       <c r="D4" s="281"/>
@@ -28281,7 +28278,7 @@
         <v>30</v>
       </c>
       <c r="M6" s="258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -35731,7 +35728,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -35742,7 +35739,7 @@
     </row>
     <row r="4" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="279" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C4" s="281"/>
       <c r="D4" s="281"/>
@@ -35800,7 +35797,7 @@
         <v>30</v>
       </c>
       <c r="M6" s="258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -37728,7 +37725,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -37739,7 +37736,7 @@
     </row>
     <row r="4" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="279" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C4" s="281"/>
       <c r="D4" s="281"/>
@@ -37797,7 +37794,7 @@
         <v>30</v>
       </c>
       <c r="M6" s="258" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -39694,7 +39691,7 @@
         <v>229</v>
       </c>
       <c r="B1" s="195" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.25">
@@ -40121,25 +40118,25 @@
         <v>425</v>
       </c>
       <c r="H1" s="195" t="s">
+        <v>440</v>
+      </c>
+      <c r="I1" s="195" t="s">
         <v>441</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="J1" s="195" t="s">
         <v>442</v>
       </c>
-      <c r="J1" s="195" t="s">
+      <c r="K1" s="195" t="s">
         <v>443</v>
       </c>
-      <c r="K1" s="195" t="s">
+      <c r="L1" s="195" t="s">
         <v>444</v>
       </c>
-      <c r="L1" s="195" t="s">
+      <c r="M1" s="195" t="s">
         <v>445</v>
       </c>
-      <c r="M1" s="195" t="s">
+      <c r="N1" s="195" t="s">
         <v>446</v>
-      </c>
-      <c r="N1" s="195" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" x14ac:dyDescent="0.25">
